--- a/site/Dayforce-Salesforce-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Salesforce-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,29 +793,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Attribute Mapper</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>DF to SF Contact</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>SF User to SF Contact</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KJ9V2T064DW0FH5T37YXT309</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KJ9V2T064DW0FH5T37YXT309</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,98 +957,54 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Salesforce-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Salesforce-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJ9V2T064DW0FH5T37YXT309</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KJ9V2T064DW0FH5T37YXT309</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Salesforce-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
